--- a/crmSource.xlsx
+++ b/crmSource.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chella\eclipse-workspace\mavenCrm\"/>
     </mc:Choice>
@@ -25,7 +25,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="201">
   <si>
     <t>Status</t>
   </si>
@@ -641,13 +641,20 @@
   </si>
   <si>
     <t>pan_02</t>
+  </si>
+  <si>
+    <t>0 Pass 1 Fail</t>
+  </si>
+  <si>
+    <t>1 Sec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -660,6 +667,12 @@
       <sz val="11"/>
       <color indexed="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -682,11 +695,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1024,87 +1038,93 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="13.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.36328125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="4.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>151</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>63</v>
       </c>
+      <c r="C2" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>200</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>157</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>63</v>
       </c>
     </row>
@@ -1118,41 +1138,44 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="31.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>145</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="4">
+        <v>185</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>149</v>
       </c>
     </row>
@@ -1166,45 +1189,45 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="3.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>16</v>
       </c>
     </row>
@@ -1218,45 +1241,45 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.6328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="3.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>16</v>
       </c>
     </row>
@@ -1270,45 +1293,45 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.36328125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="3.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>16</v>
       </c>
     </row>
@@ -1322,375 +1345,375 @@
   <dimension ref="A1:BR2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.08984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="3" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="7" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.08984375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="4.26953125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.0"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="9.26953125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.08984375"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="9.36328125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="7.26953125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="8.81640625"/>
+    <col min="15" max="17" bestFit="true" customWidth="true" width="8.36328125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="7.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="7.54296875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="7.36328125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="5.36328125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="7.1796875"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="6.7265625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.6328125"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="4.54296875"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="11.7265625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="8.08984375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="7.453125"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="7.6328125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="6.6328125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="9.90625"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="4.08984375"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="9.6328125"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="9.26953125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="10.36328125"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="4.54296875"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" width="6.54296875"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="7.7265625"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" width="10.08984375"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" width="7.7265625"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" width="8.81640625"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="6.54296875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="8.81640625"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" width="10.36328125"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" width="15.26953125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" width="11.453125"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" width="3.0"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" width="6.08984375"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" width="8.0"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" width="10.26953125"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" width="10.90625"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" width="8.6328125"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" width="3.90625"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="66" max="66" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="67" max="67" bestFit="true" customWidth="true" width="9.26953125"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" width="7.26953125"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="70" max="70" bestFit="true" customWidth="true" width="13.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>78</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AW1" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AX1" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AY1" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AZ1" t="s" s="0">
         <v>109</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BB1" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BD1" t="s" s="0">
         <v>113</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BE1" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BF1" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BG1" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BH1" t="s" s="0">
         <v>117</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BI1" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BJ1" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BK1" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BL1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BM1" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BN1" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BO1" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BP1" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BQ1" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BR1" t="s" s="0">
         <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>129</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>9876543210</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <v>1000</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <v>2024</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="0">
         <v>44123456</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>133</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="0">
         <v>600001</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AY2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BG2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BJ2" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BK2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BL2" t="s" s="0">
         <v>16</v>
       </c>
     </row>
@@ -1704,211 +1727,211 @@
   <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.26953125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.08984375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.6328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="8.08984375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="5.81640625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="6.7265625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" width="4.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="7.36328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="7.1796875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="7.54296875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="9.6328125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="8.6328125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.36328125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="10.36328125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="11.54296875"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="3.90625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="11.7265625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="8.453125"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="7.7265625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="7.26953125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="6.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" t="s" s="0">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>27</v>
       </c>
       <c r="F2" s="1">
         <v>45292</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <v>600002</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="0">
         <v>4498765</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="0">
         <v>9876500001</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>72</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" t="s" s="0">
         <v>16</v>
       </c>
     </row>
@@ -1922,102 +1945,102 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.26953125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.36328125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.7265625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.6328125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="11.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="3.7265625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.7265625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="7.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>9876543210</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="0">
         <v>5000</v>
       </c>
     </row>
@@ -2031,151 +2054,151 @@
   <dimension ref="A1:AK5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.1796875" customWidth="1"/>
-    <col min="32" max="32" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="5.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="6.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="14.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.26953125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="7.54296875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.08984375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="9.36328125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="6.7265625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="6.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.08984375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.90625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="10.36328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.81640625"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.6328125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="8.54296875"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="8.81640625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="10.36328125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="7.54296875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="11.81640625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="31" max="31" customWidth="true" width="12.1796875"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="19.81640625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="11.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>159</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>165</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" t="s" s="0">
         <v>169</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" t="s" s="0">
         <v>171</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" t="s" s="0">
         <v>173</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" t="s" s="0">
         <v>177</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" t="s" s="0">
         <v>181</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" t="s" s="0">
         <v>183</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" t="s" s="0">
         <v>184</v>
       </c>
     </row>
@@ -2183,103 +2206,103 @@
       <c r="A2" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>6369029084</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>187</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>1000</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>100</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <v>20309</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="0">
         <v>600</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="0">
         <v>73830</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>193</v>
       </c>
       <c r="S2" s="3">
         <v>46146</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="0">
         <v>39480</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>63</v>
       </c>
       <c r="W2" s="3">
         <v>46167</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="0">
         <v>93209</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="0">
         <v>2093002</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="0">
         <v>300</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="0">
         <v>124356</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="0">
         <v>0</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="0">
         <v>0</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" t="s" s="0">
         <v>195</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="0">
         <v>1000</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" t="s" s="0">
         <v>197</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" t="s" s="0">
         <v>198</v>
       </c>
     </row>
